--- a/2026/ANATOLE FRANCE/Septiembre/ANATOLE-Septiembre.xlsx
+++ b/2026/ANATOLE FRANCE/Septiembre/ANATOLE-Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53ADE65-8072-4209-9BF2-0D1B6EA13B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6721AE-098B-4182-90B6-C240FEDEC2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="167">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -481,30 +481,12 @@
     <t>Suben a $216.000 en juli0</t>
   </si>
   <si>
-    <t>VTO 17/09</t>
-  </si>
-  <si>
-    <t>PERÍODO: AGOSTO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>Transf 19/08</t>
-  </si>
-  <si>
     <t>Transf 12/08</t>
   </si>
   <si>
-    <t>Transf 05/08</t>
-  </si>
-  <si>
     <t>Transf 10/08</t>
   </si>
   <si>
-    <t>Honorarios administracion - JULIO Y AGOSTO</t>
-  </si>
-  <si>
     <t>Suplencia Sr. Roberto - Sra. Silvana</t>
   </si>
   <si>
@@ -523,7 +505,28 @@
     <t>Transf 24/08</t>
   </si>
   <si>
-    <t>Se adeuda mes de Agosto</t>
+    <t>VTO 16/10</t>
+  </si>
+  <si>
+    <t>PERÍODO: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Se adeuda mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - AGOSTO Y SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>Transf 09/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servisur - Retiro de 5 luces de emergencia obsoletas e instalacion de 5 luces led </t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -1442,7 +1445,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1473,15 +1475,36 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1494,30 +1517,60 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1533,57 +1586,6 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1602,6 +1604,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1966,7 +1971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.88671875" customWidth="1"/>
@@ -1983,11 +1988,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="127"/>
-      <c r="B1" s="181" t="s">
+      <c r="B1" s="187" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
       <c r="E1" s="128"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2001,12 +2006,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="129"/>
-      <c r="B3" s="182" t="s">
+      <c r="B3" s="188" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="183"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="189"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="132" t="s">
@@ -2024,7 +2029,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="134" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C5" s="136"/>
       <c r="D5" s="130" t="s">
@@ -2052,24 +2057,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="40"/>
-      <c r="B8" s="178" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="178"/>
+      <c r="B8" s="186" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="186"/>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="40"/>
-      <c r="B9" s="178"/>
-      <c r="C9" s="178"/>
+      <c r="B9" s="186"/>
+      <c r="C9" s="186"/>
       <c r="D9" s="40"/>
       <c r="E9" s="40"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="40"/>
-      <c r="B10" s="178"/>
-      <c r="C10" s="178"/>
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
       <c r="D10" s="40"/>
       <c r="E10" s="40"/>
     </row>
@@ -2088,34 +2093,34 @@
       <c r="E12" s="40"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="184" t="s">
+      <c r="A13" s="190" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="184"/>
-      <c r="C13" s="184"/>
-      <c r="D13" s="184"/>
-      <c r="E13" s="184"/>
+      <c r="B13" s="190"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="190"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="184"/>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
+      <c r="A14" s="190"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="190"/>
+      <c r="D14" s="190"/>
+      <c r="E14" s="190"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="184"/>
-      <c r="B15" s="184"/>
-      <c r="C15" s="184"/>
-      <c r="D15" s="184"/>
-      <c r="E15" s="184"/>
+      <c r="A15" s="190"/>
+      <c r="B15" s="190"/>
+      <c r="C15" s="190"/>
+      <c r="D15" s="190"/>
+      <c r="E15" s="190"/>
     </row>
     <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="184"/>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
+      <c r="A16" s="190"/>
+      <c r="B16" s="190"/>
+      <c r="C16" s="190"/>
+      <c r="D16" s="190"/>
+      <c r="E16" s="190"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="40"/>
@@ -2157,13 +2162,13 @@
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="179" t="s">
+      <c r="A22" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="180"/>
+      <c r="B22" s="182"/>
       <c r="C22" s="31"/>
       <c r="D22" s="104" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E22" s="31"/>
     </row>
@@ -2223,7 +2228,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="31" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -2231,12 +2236,12 @@
         <v>352000</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="31" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -2244,7 +2249,7 @@
         <v>5087</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2282,30 +2287,30 @@
       <c r="E33" s="149"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="185" t="s">
+      <c r="A34" s="177" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="186"/>
+      <c r="B34" s="178"/>
       <c r="C34" s="150"/>
-      <c r="D34" s="104">
+      <c r="D34" s="221">
         <v>50000</v>
       </c>
       <c r="E34" s="63" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="185" t="s">
-        <v>158</v>
-      </c>
-      <c r="B35" s="186"/>
+      <c r="A35" s="177" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="178"/>
       <c r="C35" s="150"/>
       <c r="D35" s="125">
         <f>216000*2</f>
         <v>432000</v>
       </c>
       <c r="E35" s="63" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G35" t="s">
         <v>150</v>
@@ -2333,10 +2338,10 @@
       <c r="E37" s="151"/>
     </row>
     <row r="38" spans="1:7" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="179" t="s">
+      <c r="A38" s="181" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="180"/>
+      <c r="B38" s="182"/>
       <c r="C38" s="152"/>
       <c r="D38" s="126">
         <v>161303</v>
@@ -2372,40 +2377,40 @@
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="150"/>
-      <c r="D41" s="155">
-        <v>805260.72</v>
+      <c r="D41" s="222">
+        <v>733506.19</v>
       </c>
       <c r="E41" s="63" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G41" s="51"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="31" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>107</v>
       </c>
       <c r="C42" s="31"/>
-      <c r="D42" s="113">
-        <v>60216.37</v>
+      <c r="D42" s="220">
+        <v>54846.84</v>
       </c>
       <c r="E42" s="63" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="31" t="str">
         <f>A42</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>109</v>
       </c>
       <c r="C43" s="31"/>
-      <c r="D43" s="113">
-        <v>111675.2</v>
+      <c r="D43" s="220">
+        <v>104388.21</v>
       </c>
       <c r="E43" s="64" t="str">
         <f>E42</f>
@@ -2415,14 +2420,14 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>108</v>
       </c>
       <c r="C44" s="31"/>
-      <c r="D44" s="113">
-        <v>6690.71</v>
+      <c r="D44" s="220">
+        <v>6094.09</v>
       </c>
       <c r="E44" s="65" t="str">
         <f>E42</f>
@@ -2438,7 +2443,7 @@
       <c r="D45" s="114"/>
       <c r="E45" s="32">
         <f>SUM(D41:D44)</f>
-        <v>983842.99999999988</v>
+        <v>898835.32999999984</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2456,24 +2461,24 @@
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
-      <c r="D47" s="113">
-        <v>221553.68</v>
+      <c r="D47" s="220">
+        <v>235592.49</v>
       </c>
       <c r="E47" s="63" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="156" t="s">
+      <c r="A48" s="155" t="s">
         <v>143</v>
       </c>
-      <c r="B48" s="157"/>
+      <c r="B48" s="156"/>
       <c r="C48" s="31"/>
       <c r="D48" s="113">
         <v>18022.7</v>
       </c>
       <c r="E48" s="63" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2487,7 +2492,7 @@
       </c>
       <c r="E49" s="65" t="str">
         <f>E47</f>
-        <v>Transf 05/08</v>
+        <v>Transf 09/09</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2499,7 +2504,7 @@
       <c r="D50" s="115"/>
       <c r="E50" s="32">
         <f>SUM(D47:D49)</f>
-        <v>1297271.7200000002</v>
+        <v>1311310.53</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2509,512 +2514,521 @@
       <c r="B51" s="147"/>
       <c r="C51" s="147"/>
       <c r="D51" s="110"/>
-      <c r="E51" s="158"/>
+      <c r="E51" s="157"/>
     </row>
     <row r="52" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="159" t="s">
+      <c r="A52" s="158" t="s">
         <v>56</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="31"/>
-      <c r="D52" s="113">
+      <c r="D52" s="220">
         <v>205400</v>
       </c>
       <c r="E52" s="63" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="159" t="s">
-        <v>132</v>
+      <c r="A53" s="158" t="s">
+        <v>166</v>
       </c>
       <c r="B53" s="143"/>
       <c r="C53" s="31"/>
-      <c r="D53" s="113">
+      <c r="D53" s="220">
+        <v>100000</v>
+      </c>
+      <c r="E53" s="124" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="158" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="143"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="113">
         <v>60000</v>
       </c>
-      <c r="E53" s="124" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="147" t="s">
+      <c r="E54" s="124" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="160">
-        <f>SUM(D52:D53)</f>
-        <v>265400</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="12" t="s">
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="159">
+        <f>SUM(D52:D54)</f>
+        <v>365400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="161"/>
-      <c r="C55" s="147"/>
-      <c r="D55" s="108"/>
-      <c r="E55" s="158"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="113">
-        <v>69000</v>
-      </c>
-      <c r="E56" s="162"/>
+      <c r="B56" s="160"/>
+      <c r="C56" s="147"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="157"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="113">
+        <v>69000</v>
+      </c>
+      <c r="E57" s="161"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="113">
         <v>105329.94</v>
       </c>
-      <c r="E57" s="35"/>
-    </row>
-    <row r="58" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="163" t="s">
+      <c r="E58" s="35"/>
+    </row>
+    <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="163"/>
-      <c r="C58" s="163"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="32">
-        <f>SUM(D56:D57)</f>
+      <c r="B59" s="162"/>
+      <c r="C59" s="162"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="32">
+        <f>SUM(D57:D58)</f>
         <v>174329.94</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="31"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="37"/>
-    </row>
     <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="164" t="s">
+      <c r="A60" s="31"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="37"/>
+    </row>
+    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="163" t="s">
         <v>45</v>
       </c>
-      <c r="B60" s="164"/>
-      <c r="C60" s="164"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="39"/>
-    </row>
-    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="165"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="20"/>
+      <c r="B61" s="163"/>
+      <c r="C61" s="163"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="39"/>
     </row>
     <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="166" t="s">
+      <c r="A62" s="164"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="20"/>
+    </row>
+    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="167"/>
-      <c r="C62" s="42"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="43">
-        <f>(SUM(E28:E60))</f>
-        <v>3721234.66</v>
-      </c>
-      <c r="F62" s="62"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="51"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="40"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
+      <c r="B63" s="166"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="43">
+        <f>(SUM(E28:E61))</f>
+        <v>3750265.8</v>
+      </c>
+      <c r="F63" s="62"/>
+      <c r="G63" s="20"/>
       <c r="H63" s="51"/>
       <c r="I63" s="51"/>
       <c r="J63" s="51"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
     </row>
-    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="40"/>
       <c r="B64" s="40"/>
       <c r="C64" s="40"/>
       <c r="D64" s="40"/>
       <c r="E64" s="40"/>
-      <c r="H64" s="67"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="139" t="s">
+      <c r="H64" s="51"/>
+      <c r="I64" s="51"/>
+      <c r="J64" s="51"/>
+      <c r="K64" s="51"/>
+      <c r="L64" s="51"/>
+    </row>
+    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="40"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="H65" s="67"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="140"/>
-      <c r="C65" s="141"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="45"/>
-    </row>
-    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="179"/>
-      <c r="B66" s="180"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="33"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="179"/>
-      <c r="B67" s="180"/>
+      <c r="B66" s="140"/>
+      <c r="C66" s="141"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="45"/>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="181"/>
+      <c r="B67" s="182"/>
       <c r="C67" s="31"/>
       <c r="D67" s="34"/>
       <c r="E67" s="33"/>
     </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="185"/>
-      <c r="B68" s="186"/>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="181"/>
+      <c r="B68" s="182"/>
       <c r="C68" s="31"/>
       <c r="D68" s="34"/>
       <c r="E68" s="33"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="142"/>
-      <c r="B69" s="168"/>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="177"/>
+      <c r="B69" s="178"/>
       <c r="C69" s="31"/>
       <c r="D69" s="34"/>
       <c r="E69" s="33"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="169"/>
-      <c r="B70" s="170"/>
-      <c r="C70" s="170"/>
-      <c r="D70" s="171"/>
-      <c r="E70" s="171">
-        <f>SUM(D66:D69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="40"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-    </row>
-    <row r="72" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="142"/>
+      <c r="B70" s="167"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="33"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="168"/>
+      <c r="B71" s="169"/>
+      <c r="C71" s="169"/>
+      <c r="D71" s="170"/>
+      <c r="E71" s="170">
+        <f>SUM(D67:D70)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="40"/>
       <c r="B72" s="40"/>
       <c r="C72" s="40"/>
       <c r="D72" s="40"/>
       <c r="E72" s="40"/>
     </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="172" t="s">
+    <row r="73" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="40"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+    </row>
+    <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="171" t="s">
         <v>19</v>
       </c>
-      <c r="B73" s="173"/>
-      <c r="C73" s="173"/>
-      <c r="D73" s="174"/>
-      <c r="E73" s="175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="40"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
-    </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="166" t="s">
+      <c r="B74" s="172"/>
+      <c r="C74" s="172"/>
+      <c r="D74" s="173"/>
+      <c r="E74" s="174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+    </row>
+    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="165" t="s">
         <v>20</v>
       </c>
-      <c r="B75" s="167"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="43">
-        <f>E70+E73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="40"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="40"/>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="176" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77" s="177">
-        <f>E62</f>
-        <v>3721234.66</v>
-      </c>
+      <c r="B76" s="166"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="43">
+        <f>E71+E74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="40"/>
+      <c r="B77" s="40"/>
       <c r="C77" s="40"/>
       <c r="D77" s="40"/>
       <c r="E77" s="40"/>
     </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="176" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="177">
-        <f>E62-E60</f>
-        <v>3721234.66</v>
+    <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="175" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" s="176">
+        <f>E63</f>
+        <v>3750265.8</v>
       </c>
       <c r="C78" s="40"/>
       <c r="D78" s="40"/>
       <c r="E78" s="40"/>
     </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="176" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" s="177">
-        <f>E75-E73</f>
-        <v>0</v>
+    <row r="79" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="175" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="176">
+        <f>E63-E61</f>
+        <v>3750265.8</v>
       </c>
       <c r="C79" s="40"/>
       <c r="D79" s="40"/>
       <c r="E79" s="40"/>
     </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="176" t="s">
-        <v>36</v>
-      </c>
-      <c r="B80" s="177">
-        <f>E75</f>
+    <row r="80" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="175" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" s="176">
+        <f>E76-E74</f>
         <v>0</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="40"/>
       <c r="E80" s="40"/>
     </row>
-    <row r="81" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="40"/>
-      <c r="B81" s="40"/>
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="175" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="176">
+        <f>E76</f>
+        <v>0</v>
+      </c>
       <c r="C81" s="40"/>
       <c r="D81" s="40"/>
       <c r="E81" s="40"/>
     </row>
-    <row r="82" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="187"/>
-      <c r="B83" s="187"/>
-      <c r="C83" s="187"/>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-    </row>
-    <row r="84" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="187"/>
-      <c r="B84" s="187"/>
-      <c r="C84" s="187"/>
-      <c r="D84" s="187"/>
-      <c r="E84" s="187"/>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="187"/>
-      <c r="B85" s="187"/>
-      <c r="C85" s="187"/>
-      <c r="D85" s="187"/>
-      <c r="E85" s="187"/>
-    </row>
-    <row r="87" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="5"/>
-    </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="28">
-        <v>0</v>
-      </c>
-      <c r="C88" s="7"/>
-    </row>
-    <row r="89" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+    <row r="82" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="40"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+    </row>
+    <row r="83" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="179"/>
+      <c r="B84" s="179"/>
+      <c r="C84" s="179"/>
+      <c r="D84" s="179"/>
+      <c r="E84" s="179"/>
+    </row>
+    <row r="85" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="179"/>
+      <c r="B85" s="179"/>
+      <c r="C85" s="179"/>
+      <c r="D85" s="179"/>
+      <c r="E85" s="179"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="179"/>
+      <c r="B86" s="179"/>
+      <c r="C86" s="179"/>
+      <c r="D86" s="179"/>
+      <c r="E86" s="179"/>
+    </row>
+    <row r="88" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="4"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="5"/>
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11"/>
+      <c r="B89" s="28">
+        <v>0</v>
+      </c>
+      <c r="C89" s="7"/>
+    </row>
+    <row r="90" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B90" s="17">
         <f>PRORRATEO!G34</f>
         <v>5558621.0700000012</v>
       </c>
-      <c r="C89" s="5"/>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
-      <c r="B90" s="17">
-        <v>0</v>
-      </c>
       <c r="C90" s="5"/>
     </row>
     <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="6"/>
+      <c r="B91" s="17">
+        <v>0</v>
+      </c>
+      <c r="C91" s="5"/>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B91" s="35">
-        <f>B120</f>
-        <v>0</v>
-      </c>
-      <c r="C91" s="5"/>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="9"/>
-      <c r="B92" s="24"/>
+      <c r="B92" s="35">
+        <f>B121</f>
+        <v>0</v>
+      </c>
       <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="50" t="s">
-        <v>41</v>
-      </c>
+      <c r="A93" s="9"/>
       <c r="B93" s="24"/>
       <c r="C93" s="5"/>
     </row>
     <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="24"/>
+      <c r="C94" s="5"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B94" s="24">
-        <f>-B78</f>
-        <v>-3721234.66</v>
-      </c>
-      <c r="C94" s="5"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="9" t="s">
+      <c r="B95" s="24">
+        <f>-B79</f>
+        <v>-3750265.8</v>
+      </c>
+      <c r="C95" s="5"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B95" s="24">
-        <f>-(B79)</f>
-        <v>0</v>
-      </c>
-      <c r="C95" s="5"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="10" t="s">
+      <c r="B96" s="24">
+        <f>-(B80)</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="5"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B96" s="28">
-        <f>SUM(B88:B95)</f>
-        <v>1837386.4100000011</v>
-      </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="20"/>
-    </row>
-    <row r="97" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="18"/>
+      <c r="B97" s="28">
+        <f>SUM(B89:B96)</f>
+        <v>1808355.2700000014</v>
+      </c>
       <c r="C97" s="8"/>
       <c r="D97" s="20"/>
-      <c r="E97" s="53"/>
-      <c r="F97" s="54"/>
-    </row>
-    <row r="98" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="19"/>
+    </row>
+    <row r="98" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="18"/>
       <c r="C98" s="8"/>
-    </row>
-    <row r="99" spans="1:6" s="15" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99"/>
-      <c r="B99" s="18"/>
-      <c r="C99" s="14"/>
-    </row>
-    <row r="100" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="56" t="s">
+      <c r="D98" s="20"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="54"/>
+    </row>
+    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="19"/>
+      <c r="C99" s="8"/>
+    </row>
+    <row r="100" spans="1:6" s="15" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="14"/>
+    </row>
+    <row r="101" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="B100" s="94">
+      <c r="B101" s="94">
         <v>874049.42000000365</v>
       </c>
-      <c r="C100" s="14"/>
-      <c r="D100" s="23"/>
-      <c r="E100" s="20"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B101" s="103">
-        <f>-B78</f>
-        <v>-3721234.66</v>
-      </c>
+      <c r="C101" s="14"/>
+      <c r="D101" s="23"/>
+      <c r="E101" s="20"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B102" s="60">
+        <v>46</v>
+      </c>
+      <c r="B102" s="103">
         <f>-B79</f>
-        <v>0</v>
+        <v>-3750265.8</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B103" s="60">
-        <f>B120</f>
+        <f>-B80</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B104" s="60">
+        <f>B121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B104" s="61">
+      <c r="B105" s="61">
         <f>PRORRATEO!G34</f>
         <v>5558621.0700000012</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="58" t="s">
+    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B105" s="59">
-        <f>SUM(B100:C104)</f>
-        <v>2711435.8300000047</v>
-      </c>
-      <c r="D105" s="20"/>
-      <c r="E105" s="20"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="57"/>
-      <c r="B106" s="57"/>
+      <c r="B106" s="59">
+        <f>SUM(B101:C105)</f>
+        <v>2682404.6900000051</v>
+      </c>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="57"/>
       <c r="B107" s="57"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="189" t="s">
+      <c r="A108" s="57"/>
+      <c r="B108" s="57"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="183" t="s">
         <v>149</v>
       </c>
-      <c r="B108" s="189"/>
-    </row>
-    <row r="109" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="190"/>
-      <c r="B109" s="190"/>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="190"/>
-      <c r="B110" s="190"/>
-    </row>
-    <row r="111" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="191"/>
-      <c r="B111" s="191"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="57"/>
-      <c r="B112" s="57"/>
+      <c r="B109" s="183"/>
+    </row>
+    <row r="110" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="184"/>
+      <c r="B110" s="184"/>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="184"/>
+      <c r="B111" s="184"/>
+    </row>
+    <row r="112" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="185"/>
+      <c r="B112" s="185"/>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="57"/>
@@ -3024,91 +3038,95 @@
       <c r="A114" s="57"/>
       <c r="B114" s="57"/>
     </row>
-    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="188" t="s">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="57"/>
+      <c r="B115" s="57"/>
+    </row>
+    <row r="116" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="B116" s="188"/>
-      <c r="C116" s="188"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="188"/>
-      <c r="B117" s="188"/>
-      <c r="C117" s="188"/>
-    </row>
-    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="47"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="13">
+      <c r="B117" s="180"/>
+      <c r="C117" s="180"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="180"/>
+      <c r="B118" s="180"/>
+      <c r="C118" s="180"/>
+    </row>
+    <row r="119" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="47"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13">
         <v>40000</v>
       </c>
-      <c r="E118" s="62"/>
-    </row>
-    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="47"/>
-      <c r="B119" s="49"/>
-      <c r="C119" s="46"/>
-      <c r="D119" s="62"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="21" t="s">
+      <c r="E119" s="62"/>
+    </row>
+    <row r="120" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="47"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="46"/>
+      <c r="D120" s="62"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B120" s="48">
-        <f>SUM(B118:B119)</f>
-        <v>0</v>
-      </c>
-      <c r="C120" s="22"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M121" s="2"/>
-    </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="187"/>
-      <c r="B122" s="187"/>
-      <c r="C122" s="187"/>
-      <c r="D122" s="187"/>
-      <c r="E122" s="187"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="187"/>
-      <c r="B123" s="187"/>
-      <c r="C123" s="187"/>
-      <c r="D123" s="187"/>
-      <c r="E123" s="187"/>
+      <c r="B121" s="48">
+        <f>SUM(B119:B120)</f>
+        <v>0</v>
+      </c>
+      <c r="C121" s="22"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M122" s="2"/>
+    </row>
+    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="179"/>
+      <c r="B123" s="179"/>
+      <c r="C123" s="179"/>
+      <c r="D123" s="179"/>
+      <c r="E123" s="179"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="187"/>
-      <c r="B124" s="187"/>
-      <c r="C124" s="187"/>
-      <c r="D124" s="187"/>
-      <c r="E124" s="187"/>
+      <c r="A124" s="179"/>
+      <c r="B124" s="179"/>
+      <c r="C124" s="179"/>
+      <c r="D124" s="179"/>
+      <c r="E124" s="179"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125" s="187"/>
-      <c r="B125" s="187"/>
-      <c r="C125" s="187"/>
-      <c r="D125" s="187"/>
-      <c r="E125" s="187"/>
+      <c r="A125" s="179"/>
+      <c r="B125" s="179"/>
+      <c r="C125" s="179"/>
+      <c r="D125" s="179"/>
+      <c r="E125" s="179"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="179"/>
+      <c r="B126" s="179"/>
+      <c r="C126" s="179"/>
+      <c r="D126" s="179"/>
+      <c r="E126" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A122:E125"/>
-    <mergeCell ref="A116:C117"/>
-    <mergeCell ref="A83:E85"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A108:B111"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A123:E126"/>
+    <mergeCell ref="A117:C118"/>
+    <mergeCell ref="A84:E86"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A109:B112"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3144,14 +3162,14 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3194,110 +3212,110 @@
       <c r="M3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="206" t="s">
+      <c r="A4" s="200" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="207"/>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
-      <c r="M4" s="208"/>
+      <c r="B4" s="201"/>
+      <c r="C4" s="201"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
+      <c r="M4" s="202"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="209"/>
-      <c r="B5" s="210"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="210"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="210"/>
-      <c r="K5" s="210"/>
-      <c r="L5" s="210"/>
-      <c r="M5" s="211"/>
+      <c r="A5" s="203"/>
+      <c r="B5" s="204"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="204"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="204"/>
+      <c r="J5" s="204"/>
+      <c r="K5" s="204"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="205"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="212"/>
-      <c r="B6" s="213"/>
-      <c r="C6" s="213"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="213"/>
-      <c r="G6" s="213"/>
-      <c r="H6" s="213"/>
-      <c r="I6" s="213"/>
-      <c r="J6" s="213"/>
-      <c r="K6" s="213"/>
-      <c r="L6" s="213"/>
-      <c r="M6" s="214"/>
+      <c r="A6" s="206"/>
+      <c r="B6" s="207"/>
+      <c r="C6" s="207"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="207"/>
+      <c r="G6" s="207"/>
+      <c r="H6" s="207"/>
+      <c r="I6" s="207"/>
+      <c r="J6" s="207"/>
+      <c r="K6" s="207"/>
+      <c r="L6" s="207"/>
+      <c r="M6" s="208"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="192" t="s">
+      <c r="A7" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="192" t="s">
+      <c r="B7" s="195" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="192" t="s">
+      <c r="C7" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="192" t="s">
+      <c r="D7" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="192" t="s">
+      <c r="E7" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="200" t="s">
+      <c r="F7" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="192" t="s">
+      <c r="G7" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="202" t="s">
+      <c r="H7" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="200" t="s">
+      <c r="I7" s="193" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="200" t="s">
+      <c r="J7" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="204" t="s">
+      <c r="K7" s="198" t="s">
         <v>58</v>
       </c>
       <c r="L7" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="198" t="s">
+      <c r="M7" s="191" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="192"/>
-      <c r="B8" s="193"/>
-      <c r="C8" s="192"/>
-      <c r="D8" s="193"/>
-      <c r="E8" s="192"/>
-      <c r="F8" s="201"/>
-      <c r="G8" s="192"/>
-      <c r="H8" s="203"/>
-      <c r="I8" s="201"/>
-      <c r="J8" s="201"/>
-      <c r="K8" s="205"/>
+      <c r="A8" s="195"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="194"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="194"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="199"/>
       <c r="L8" s="30" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 17/09</v>
-      </c>
-      <c r="M8" s="198"/>
+        <v>VTO 16/10</v>
+      </c>
+      <c r="M8" s="191"/>
     </row>
     <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="69">
@@ -4402,7 +4420,7 @@
         <v>0.21000000000000005</v>
       </c>
       <c r="O29" s="79" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -4562,8 +4580,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="194"/>
-      <c r="B33" s="195"/>
+      <c r="A33" s="210"/>
+      <c r="B33" s="211"/>
       <c r="C33" s="84"/>
       <c r="D33" s="84"/>
       <c r="E33" s="70"/>
@@ -4578,11 +4596,11 @@
       <c r="N33" s="20"/>
     </row>
     <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="196" t="s">
+      <c r="A34" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="196"/>
-      <c r="C34" s="197"/>
+      <c r="B34" s="212"/>
+      <c r="C34" s="213"/>
       <c r="D34" s="86"/>
       <c r="E34" s="93">
         <f t="shared" ref="E34:K34" si="11">SUM(E9:E33)</f>
@@ -4627,82 +4645,90 @@
     </row>
     <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="187" t="str">
+      <c r="C37" s="179" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="187"/>
-      <c r="E37" s="187"/>
-      <c r="F37" s="187"/>
-      <c r="G37" s="187"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="187"/>
-      <c r="J37" s="187"/>
-      <c r="K37" s="187"/>
-      <c r="L37" s="187"/>
+      <c r="D37" s="179"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="179"/>
+      <c r="I37" s="179"/>
+      <c r="J37" s="179"/>
+      <c r="K37" s="179"/>
+      <c r="L37" s="179"/>
     </row>
     <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="187"/>
-      <c r="D38" s="187"/>
-      <c r="E38" s="187"/>
-      <c r="F38" s="187"/>
-      <c r="G38" s="187"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="187"/>
-      <c r="K38" s="187"/>
-      <c r="L38" s="187"/>
+      <c r="C38" s="179"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="179"/>
+      <c r="I38" s="179"/>
+      <c r="J38" s="179"/>
+      <c r="K38" s="179"/>
+      <c r="L38" s="179"/>
     </row>
     <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="187"/>
-      <c r="D39" s="187"/>
-      <c r="E39" s="187"/>
-      <c r="F39" s="187"/>
-      <c r="G39" s="187"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="187"/>
-      <c r="J39" s="187"/>
-      <c r="K39" s="187"/>
-      <c r="L39" s="187"/>
+      <c r="C39" s="179"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="179"/>
+      <c r="F39" s="179"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="179"/>
+      <c r="I39" s="179"/>
+      <c r="J39" s="179"/>
+      <c r="K39" s="179"/>
+      <c r="L39" s="179"/>
     </row>
     <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="187"/>
-      <c r="D40" s="187"/>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187"/>
-      <c r="G40" s="187"/>
-      <c r="H40" s="187"/>
-      <c r="I40" s="187"/>
-      <c r="J40" s="187"/>
-      <c r="K40" s="187"/>
-      <c r="L40" s="187"/>
+      <c r="C40" s="179"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="179"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
+      <c r="L40" s="179"/>
     </row>
     <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="187"/>
-      <c r="D41" s="187"/>
-      <c r="E41" s="187"/>
-      <c r="F41" s="187"/>
-      <c r="G41" s="187"/>
-      <c r="H41" s="187"/>
-      <c r="I41" s="187"/>
-      <c r="J41" s="187"/>
-      <c r="K41" s="187"/>
-      <c r="L41" s="187"/>
+      <c r="C41" s="179"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="179"/>
+      <c r="F41" s="179"/>
+      <c r="G41" s="179"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="179"/>
+      <c r="L41" s="179"/>
     </row>
     <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="187"/>
-      <c r="D42" s="187"/>
-      <c r="E42" s="187"/>
-      <c r="F42" s="187"/>
-      <c r="G42" s="187"/>
-      <c r="H42" s="187"/>
-      <c r="I42" s="187"/>
-      <c r="J42" s="187"/>
-      <c r="K42" s="187"/>
-      <c r="L42" s="187"/>
+      <c r="C42" s="179"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="179"/>
+      <c r="F42" s="179"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
+      <c r="L42" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4712,14 +4738,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4754,36 +4772,36 @@
       <c r="G5" s="118"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="215"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="217"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="215"/>
+      <c r="G6" s="216"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="215"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="217"/>
+      <c r="B7" s="214"/>
+      <c r="C7" s="215"/>
+      <c r="D7" s="215"/>
+      <c r="E7" s="215"/>
+      <c r="F7" s="215"/>
+      <c r="G7" s="216"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="215"/>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="217"/>
+      <c r="B8" s="214"/>
+      <c r="C8" s="215"/>
+      <c r="D8" s="215"/>
+      <c r="E8" s="215"/>
+      <c r="F8" s="215"/>
+      <c r="G8" s="216"/>
     </row>
     <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="218"/>
-      <c r="C9" s="219"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="G9" s="220"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="218"/>
+      <c r="D9" s="218"/>
+      <c r="E9" s="218"/>
+      <c r="F9" s="218"/>
+      <c r="G9" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/ANATOLE FRANCE/Septiembre/ANATOLE-Septiembre.xlsx
+++ b/2026/ANATOLE FRANCE/Septiembre/ANATOLE-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6721AE-098B-4182-90B6-C240FEDEC2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CB8415-ACD1-4C0F-8301-61F16ABEAEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -481,21 +486,12 @@
     <t>Suben a $216.000 en juli0</t>
   </si>
   <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Transf 10/08</t>
-  </si>
-  <si>
     <t>Suplencia Sr. Roberto - Sra. Silvana</t>
   </si>
   <si>
     <t>Seguro Sra. Silvana</t>
   </si>
   <si>
-    <t>Transf 28/08</t>
-  </si>
-  <si>
     <t>Caludio luis</t>
   </si>
   <si>
@@ -511,15 +507,9 @@
     <t>PERÍODO: SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Se adeuda mes de SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Sindicatos mes de SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Honorarios administracion - AGOSTO Y SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Transf 11/09</t>
   </si>
   <si>
@@ -527,6 +517,21 @@
   </si>
   <si>
     <t xml:space="preserve">Servisur - Retiro de 5 luces de emergencia obsoletas e instalacion de 5 luces led </t>
+  </si>
+  <si>
+    <t>Mes de agosto</t>
+  </si>
+  <si>
+    <t>Transf 10/09</t>
+  </si>
+  <si>
+    <t>Honorarios administracion -  SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Transf 14/09</t>
+  </si>
+  <si>
+    <t>Transf 28/09</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1224,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -1475,6 +1480,27 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1487,12 +1513,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1502,20 +1522,23 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1529,9 +1552,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1571,21 +1591,6 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1604,9 +1609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1685,9 +1688,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1725,9 +1728,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1760,9 +1763,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1795,9 +1815,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1972,30 +2009,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="127"/>
-      <c r="B1" s="187" t="s">
+      <c r="B1" s="180" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
       <c r="E1" s="128"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="129"/>
       <c r="B2" s="130" t="s">
         <v>26</v>
@@ -2004,16 +2041,16 @@
       <c r="D2" s="130"/>
       <c r="E2" s="131"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="129"/>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="181" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="189"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="182"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="132" t="s">
         <v>0</v>
       </c>
@@ -2024,12 +2061,12 @@
       <c r="D4" s="134"/>
       <c r="E4" s="135"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="129" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="134" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C5" s="136"/>
       <c r="D5" s="130" t="s">
@@ -2037,7 +2074,7 @@
       </c>
       <c r="E5" s="137"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="132" t="s">
         <v>55</v>
       </c>
@@ -2048,102 +2085,102 @@
       </c>
       <c r="E6" s="135"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="40"/>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
-      <c r="B8" s="186" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="186"/>
+      <c r="B8" s="177" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="177"/>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="40"/>
-      <c r="B9" s="186"/>
-      <c r="C9" s="186"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="177"/>
       <c r="D9" s="40"/>
       <c r="E9" s="40"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="40"/>
-      <c r="B10" s="186"/>
-      <c r="C10" s="186"/>
+      <c r="B10" s="177"/>
+      <c r="C10" s="177"/>
       <c r="D10" s="40"/>
       <c r="E10" s="40"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="40"/>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
       <c r="D11" s="40"/>
       <c r="E11" s="40"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="40"/>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
       <c r="D12" s="40"/>
       <c r="E12" s="40"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="190" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="183" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="190"/>
-      <c r="C13" s="190"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="190"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="190"/>
-      <c r="B14" s="190"/>
-      <c r="C14" s="190"/>
-      <c r="D14" s="190"/>
-      <c r="E14" s="190"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="190"/>
-      <c r="B15" s="190"/>
-      <c r="C15" s="190"/>
-      <c r="D15" s="190"/>
-      <c r="E15" s="190"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="190"/>
-      <c r="B16" s="190"/>
-      <c r="C16" s="190"/>
-      <c r="D16" s="190"/>
-      <c r="E16" s="190"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="183"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="183"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="183"/>
+      <c r="B15" s="183"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="183"/>
+      <c r="B16" s="183"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="40"/>
       <c r="B17" s="40"/>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
       <c r="E17" s="40"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="138"/>
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
       <c r="D18" s="40"/>
       <c r="E18" s="40"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="40"/>
       <c r="B19" s="40"/>
       <c r="C19" s="40"/>
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
         <v>9</v>
       </c>
@@ -2152,7 +2189,7 @@
       <c r="D20" s="44"/>
       <c r="E20" s="45"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>31</v>
       </c>
@@ -2161,27 +2198,31 @@
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="181" t="s">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="178" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="182"/>
+      <c r="B22" s="179"/>
       <c r="C22" s="31"/>
-      <c r="D22" s="104" t="s">
-        <v>161</v>
-      </c>
-      <c r="E22" s="31"/>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="104">
+        <v>1218818.6100000001</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>111</v>
       </c>
       <c r="B23" s="143"/>
       <c r="C23" s="31"/>
-      <c r="D23" s="104"/>
+      <c r="D23" s="104">
+        <v>-301657.61</v>
+      </c>
       <c r="E23" s="31"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>112</v>
       </c>
@@ -2190,7 +2231,7 @@
       <c r="D24" s="104"/>
       <c r="E24" s="31"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="144" t="s">
         <v>32</v>
       </c>
@@ -2198,12 +2239,12 @@
       <c r="C25" s="144"/>
       <c r="D25" s="105">
         <f>SUM(D22:D24)</f>
-        <v>0</v>
+        <v>917161.00000000012</v>
       </c>
       <c r="E25" s="145"/>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
         <v>39</v>
       </c>
@@ -2212,47 +2253,47 @@
       <c r="D26" s="104"/>
       <c r="E26" s="31"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="146"/>
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="104"/>
       <c r="E27" s="31"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="104"/>
       <c r="E28" s="31"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="106">
-        <v>352000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="106">
-        <v>5087</v>
+        <v>0</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="144" t="s">
         <v>32</v>
       </c>
@@ -2260,11 +2301,11 @@
       <c r="C31" s="144"/>
       <c r="D31" s="107">
         <f>SUM(D26:D30)</f>
-        <v>357087</v>
+        <v>0</v>
       </c>
       <c r="E31" s="145"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="147" t="s">
         <v>1</v>
       </c>
@@ -2273,11 +2314,11 @@
       <c r="D32" s="108"/>
       <c r="E32" s="148">
         <f>D25+D31</f>
-        <v>357087</v>
+        <v>917161.00000000012</v>
       </c>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>18</v>
       </c>
@@ -2286,37 +2327,37 @@
       <c r="D33" s="109"/>
       <c r="E33" s="149"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="177" t="s">
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="184" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="178"/>
+      <c r="B34" s="185"/>
       <c r="C34" s="150"/>
-      <c r="D34" s="221">
+      <c r="D34" s="104">
         <v>50000</v>
       </c>
       <c r="E34" s="63" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="184" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="177" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" s="178"/>
+      <c r="B35" s="185"/>
       <c r="C35" s="150"/>
       <c r="D35" s="125">
-        <f>216000*2</f>
-        <v>432000</v>
+        <f>216000</f>
+        <v>216000</v>
       </c>
       <c r="E35" s="63" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G35" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="147" t="s">
         <v>15</v>
       </c>
@@ -2325,10 +2366,10 @@
       <c r="D36" s="110"/>
       <c r="E36" s="148">
         <f>SUM(D34:D35)</f>
-        <v>482000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>266000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>29</v>
       </c>
@@ -2337,11 +2378,11 @@
       <c r="D37" s="111"/>
       <c r="E37" s="151"/>
     </row>
-    <row r="38" spans="1:7" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="181" t="s">
+    <row r="38" spans="1:7" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="178" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="182"/>
+      <c r="B38" s="179"/>
       <c r="C38" s="152"/>
       <c r="D38" s="126">
         <v>161303</v>
@@ -2350,7 +2391,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="147" t="s">
         <v>2</v>
       </c>
@@ -2362,7 +2403,7 @@
         <v>161303</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>16</v>
       </c>
@@ -2371,36 +2412,36 @@
       <c r="D40" s="112"/>
       <c r="E40" s="154"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
         <v>42</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="150"/>
-      <c r="D41" s="222">
+      <c r="D41" s="220">
         <v>733506.19</v>
       </c>
       <c r="E41" s="63" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G41" s="51"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>107</v>
       </c>
       <c r="C42" s="31"/>
-      <c r="D42" s="220">
+      <c r="D42" s="113">
         <v>54846.84</v>
       </c>
       <c r="E42" s="63" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="31" t="str">
         <f>A42</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
@@ -2409,15 +2450,15 @@
         <v>109</v>
       </c>
       <c r="C43" s="31"/>
-      <c r="D43" s="220">
+      <c r="D43" s="113">
         <v>104388.21</v>
       </c>
       <c r="E43" s="64" t="str">
         <f>E42</f>
-        <v>Transf 12/08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Transf 14/09</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="31" t="str">
         <f>A43</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
@@ -2426,15 +2467,15 @@
         <v>108</v>
       </c>
       <c r="C44" s="31"/>
-      <c r="D44" s="220">
+      <c r="D44" s="113">
         <v>6094.09</v>
       </c>
       <c r="E44" s="65" t="str">
         <f>E42</f>
-        <v>Transf 12/08</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Transf 14/09</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="147" t="s">
         <v>3</v>
       </c>
@@ -2446,7 +2487,7 @@
         <v>898835.32999999984</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>17</v>
       </c>
@@ -2455,33 +2496,33 @@
       <c r="D46" s="112"/>
       <c r="E46" s="154"/>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="31" t="s">
         <v>105</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
-      <c r="D47" s="220">
-        <v>235592.49</v>
+      <c r="D47" s="113">
+        <v>236681.52</v>
       </c>
       <c r="E47" s="63" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="155" t="s">
         <v>143</v>
       </c>
       <c r="B48" s="156"/>
       <c r="C48" s="31"/>
       <c r="D48" s="113">
-        <v>18022.7</v>
+        <v>18449.13</v>
       </c>
       <c r="E48" s="63" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="142" t="s">
         <v>106</v>
       </c>
@@ -2495,7 +2536,7 @@
         <v>Transf 09/09</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="147" t="s">
         <v>4</v>
       </c>
@@ -2504,10 +2545,10 @@
       <c r="D50" s="115"/>
       <c r="E50" s="32">
         <f>SUM(D47:D49)</f>
-        <v>1311310.53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1312825.99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>142</v>
       </c>
@@ -2516,33 +2557,33 @@
       <c r="D51" s="110"/>
       <c r="E51" s="157"/>
     </row>
-    <row r="52" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="158" t="s">
         <v>56</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="31"/>
-      <c r="D52" s="220">
+      <c r="D52" s="113">
         <v>205400</v>
       </c>
       <c r="E52" s="63" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="158" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B53" s="143"/>
       <c r="C53" s="31"/>
-      <c r="D53" s="220">
+      <c r="D53" s="113">
         <v>100000</v>
       </c>
       <c r="E53" s="124" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="158" t="s">
         <v>132</v>
       </c>
@@ -2552,10 +2593,10 @@
         <v>60000</v>
       </c>
       <c r="E54" s="124" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="147" t="s">
         <v>8</v>
       </c>
@@ -2567,7 +2608,7 @@
         <v>365400</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2617,7 @@
       <c r="D56" s="108"/>
       <c r="E56" s="157"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="31" t="s">
         <v>52</v>
       </c>
@@ -2587,18 +2628,19 @@
       </c>
       <c r="E57" s="161"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="31" t="s">
         <v>51</v>
       </c>
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
       <c r="D58" s="113">
-        <v>105329.94</v>
+        <f>85031.69+93</f>
+        <v>85124.69</v>
       </c>
       <c r="E58" s="35"/>
     </row>
-    <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="162" t="s">
         <v>15</v>
       </c>
@@ -2607,26 +2649,29 @@
       <c r="D59" s="36"/>
       <c r="E59" s="32">
         <f>SUM(D57:D58)</f>
-        <v>174329.94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>154124.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="31"/>
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
       <c r="D60" s="31"/>
       <c r="E60" s="37"/>
     </row>
-    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="163" t="s">
         <v>45</v>
       </c>
       <c r="B61" s="163"/>
       <c r="C61" s="163"/>
       <c r="D61" s="38"/>
-      <c r="E61" s="39"/>
-    </row>
-    <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E61" s="39">
+        <f>4638395.66-4075557.01-93</f>
+        <v>562745.65000000037</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="164"/>
       <c r="B62" s="40"/>
       <c r="C62" s="40"/>
@@ -2634,7 +2679,7 @@
       <c r="E62" s="41"/>
       <c r="F62" s="20"/>
     </row>
-    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="165" t="s">
         <v>12</v>
       </c>
@@ -2643,7 +2688,7 @@
       <c r="D63" s="42"/>
       <c r="E63" s="43">
         <f>(SUM(E28:E61))</f>
-        <v>3750265.8</v>
+        <v>4638395.66</v>
       </c>
       <c r="F63" s="62"/>
       <c r="G63" s="20"/>
@@ -2653,7 +2698,7 @@
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="40"/>
       <c r="B64" s="40"/>
       <c r="C64" s="40"/>
@@ -2665,7 +2710,7 @@
       <c r="K64" s="51"/>
       <c r="L64" s="51"/>
     </row>
-    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="40"/>
       <c r="B65" s="40"/>
       <c r="C65" s="40"/>
@@ -2673,7 +2718,7 @@
       <c r="E65" s="40"/>
       <c r="H65" s="67"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="139" t="s">
         <v>40</v>
       </c>
@@ -2682,35 +2727,35 @@
       <c r="D66" s="44"/>
       <c r="E66" s="45"/>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="181"/>
-      <c r="B67" s="182"/>
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="178"/>
+      <c r="B67" s="179"/>
       <c r="C67" s="31"/>
       <c r="D67" s="34"/>
       <c r="E67" s="33"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="181"/>
-      <c r="B68" s="182"/>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="178"/>
+      <c r="B68" s="179"/>
       <c r="C68" s="31"/>
       <c r="D68" s="34"/>
       <c r="E68" s="33"/>
     </row>
-    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="177"/>
-      <c r="B69" s="178"/>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="184"/>
+      <c r="B69" s="185"/>
       <c r="C69" s="31"/>
       <c r="D69" s="34"/>
       <c r="E69" s="33"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="167"/>
       <c r="C70" s="31"/>
       <c r="D70" s="34"/>
       <c r="E70" s="33"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="168"/>
       <c r="B71" s="169"/>
       <c r="C71" s="169"/>
@@ -2720,21 +2765,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="40"/>
       <c r="B72" s="40"/>
       <c r="C72" s="40"/>
       <c r="D72" s="40"/>
       <c r="E72" s="40"/>
     </row>
-    <row r="73" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="40"/>
       <c r="B73" s="40"/>
       <c r="C73" s="40"/>
       <c r="D73" s="40"/>
       <c r="E73" s="40"/>
     </row>
-    <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="171" t="s">
         <v>19</v>
       </c>
@@ -2745,14 +2790,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="40"/>
       <c r="B75" s="40"/>
       <c r="C75" s="40"/>
       <c r="D75" s="40"/>
       <c r="E75" s="40"/>
     </row>
-    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="165" t="s">
         <v>20</v>
       </c>
@@ -2764,38 +2809,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="40"/>
       <c r="B77" s="40"/>
       <c r="C77" s="40"/>
       <c r="D77" s="40"/>
       <c r="E77" s="40"/>
     </row>
-    <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="175" t="s">
         <v>13</v>
       </c>
       <c r="B78" s="176">
         <f>E63</f>
-        <v>3750265.8</v>
+        <v>4638395.66</v>
       </c>
       <c r="C78" s="40"/>
       <c r="D78" s="40"/>
       <c r="E78" s="40"/>
     </row>
-    <row r="79" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="175" t="s">
         <v>14</v>
       </c>
       <c r="B79" s="176">
         <f>E63-E61</f>
-        <v>3750265.8</v>
+        <v>4075650.01</v>
       </c>
       <c r="C79" s="40"/>
       <c r="D79" s="40"/>
       <c r="E79" s="40"/>
     </row>
-    <row r="80" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="175" t="s">
         <v>21</v>
       </c>
@@ -2807,7 +2852,7 @@
       <c r="D80" s="40"/>
       <c r="E80" s="40"/>
     </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="175" t="s">
         <v>36</v>
       </c>
@@ -2819,65 +2864,65 @@
       <c r="D81" s="40"/>
       <c r="E81" s="40"/>
     </row>
-    <row r="82" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="40"/>
       <c r="B82" s="40"/>
       <c r="C82" s="40"/>
       <c r="D82" s="40"/>
       <c r="E82" s="40"/>
     </row>
-    <row r="83" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="179"/>
-      <c r="B84" s="179"/>
-      <c r="C84" s="179"/>
-      <c r="D84" s="179"/>
-      <c r="E84" s="179"/>
-    </row>
-    <row r="85" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="179"/>
-      <c r="B85" s="179"/>
-      <c r="C85" s="179"/>
-      <c r="D85" s="179"/>
-      <c r="E85" s="179"/>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="179"/>
-      <c r="B86" s="179"/>
-      <c r="C86" s="179"/>
-      <c r="D86" s="179"/>
-      <c r="E86" s="179"/>
-    </row>
-    <row r="88" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="186"/>
+      <c r="B84" s="186"/>
+      <c r="C84" s="186"/>
+      <c r="D84" s="186"/>
+      <c r="E84" s="186"/>
+    </row>
+    <row r="85" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="186"/>
+      <c r="B85" s="186"/>
+      <c r="C85" s="186"/>
+      <c r="D85" s="186"/>
+      <c r="E85" s="186"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="186"/>
+      <c r="B86" s="186"/>
+      <c r="C86" s="186"/>
+      <c r="D86" s="186"/>
+      <c r="E86" s="186"/>
+    </row>
+    <row r="88" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="52"/>
       <c r="C88" s="5"/>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
       <c r="B89" s="28">
         <v>0</v>
       </c>
       <c r="C89" s="7"/>
     </row>
-    <row r="90" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B90" s="17">
         <f>PRORRATEO!G34</f>
-        <v>5558621.0700000012</v>
+        <v>6298862.7000000011</v>
       </c>
       <c r="C90" s="5"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="17">
         <v>0</v>
       </c>
       <c r="C91" s="5"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>37</v>
       </c>
@@ -2887,29 +2932,29 @@
       </c>
       <c r="C92" s="5"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9"/>
       <c r="B93" s="24"/>
       <c r="C93" s="5"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="50" t="s">
         <v>41</v>
       </c>
       <c r="B94" s="24"/>
       <c r="C94" s="5"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="16" t="s">
         <v>22</v>
       </c>
       <c r="B95" s="24">
         <f>-B79</f>
-        <v>-3750265.8</v>
+        <v>-4075650.01</v>
       </c>
       <c r="C95" s="5"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>23</v>
       </c>
@@ -2919,54 +2964,54 @@
       </c>
       <c r="C96" s="5"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B97" s="28">
         <f>SUM(B89:B96)</f>
-        <v>1808355.2700000014</v>
+        <v>2223212.6900000013</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="20"/>
     </row>
-    <row r="98" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="18"/>
       <c r="C98" s="8"/>
       <c r="D98" s="20"/>
       <c r="E98" s="53"/>
       <c r="F98" s="54"/>
     </row>
-    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="19"/>
       <c r="C99" s="8"/>
     </row>
-    <row r="100" spans="1:6" s="15" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" s="15" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="B100" s="18"/>
       <c r="C100" s="14"/>
     </row>
-    <row r="101" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="56" t="s">
         <v>125</v>
       </c>
       <c r="B101" s="94">
-        <v>874049.42000000365</v>
+        <v>2711435.8300000047</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="23"/>
       <c r="E101" s="20"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="26" t="s">
         <v>46</v>
       </c>
       <c r="B102" s="103">
         <f>-B79</f>
-        <v>-3750265.8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-4075650.01</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
         <v>47</v>
       </c>
@@ -2975,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="26" t="s">
         <v>50</v>
       </c>
@@ -2984,78 +3029,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
         <v>48</v>
       </c>
       <c r="B105" s="61">
         <f>PRORRATEO!G34</f>
-        <v>5558621.0700000012</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>6298862.7000000011</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="58" t="s">
         <v>43</v>
       </c>
       <c r="B106" s="59">
         <f>SUM(B101:C105)</f>
-        <v>2682404.6900000051</v>
+        <v>4934648.5200000061</v>
       </c>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="57"/>
       <c r="B107" s="57"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="57"/>
       <c r="B108" s="57"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="183" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="188" t="s">
         <v>149</v>
       </c>
-      <c r="B109" s="183"/>
-    </row>
-    <row r="110" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="184"/>
-      <c r="B110" s="184"/>
-    </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="184"/>
-      <c r="B111" s="184"/>
-    </row>
-    <row r="112" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="185"/>
-      <c r="B112" s="185"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B109" s="188"/>
+    </row>
+    <row r="110" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="189"/>
+      <c r="B110" s="189"/>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="189"/>
+      <c r="B111" s="189"/>
+    </row>
+    <row r="112" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="190"/>
+      <c r="B112" s="190"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="57"/>
       <c r="B113" s="57"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="57"/>
       <c r="B114" s="57"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="57"/>
       <c r="B115" s="57"/>
     </row>
-    <row r="116" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="180" t="s">
+    <row r="116" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="187" t="s">
         <v>30</v>
       </c>
-      <c r="B117" s="180"/>
-      <c r="C117" s="180"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="180"/>
-      <c r="B118" s="180"/>
-      <c r="C118" s="180"/>
-    </row>
-    <row r="119" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="187"/>
+      <c r="C117" s="187"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="187"/>
+      <c r="B118" s="187"/>
+      <c r="C118" s="187"/>
+    </row>
+    <row r="119" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="47"/>
       <c r="B119" s="13"/>
       <c r="C119" s="13">
@@ -3063,13 +3108,13 @@
       </c>
       <c r="E119" s="62"/>
     </row>
-    <row r="120" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="47"/>
       <c r="B120" s="49"/>
       <c r="C120" s="46"/>
       <c r="D120" s="62"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="21" t="s">
         <v>8</v>
       </c>
@@ -3079,44 +3124,39 @@
       </c>
       <c r="C121" s="22"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M122" s="2"/>
     </row>
-    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="179"/>
-      <c r="B123" s="179"/>
-      <c r="C123" s="179"/>
-      <c r="D123" s="179"/>
-      <c r="E123" s="179"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="179"/>
-      <c r="B124" s="179"/>
-      <c r="C124" s="179"/>
-      <c r="D124" s="179"/>
-      <c r="E124" s="179"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125" s="179"/>
-      <c r="B125" s="179"/>
-      <c r="C125" s="179"/>
-      <c r="D125" s="179"/>
-      <c r="E125" s="179"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126" s="179"/>
-      <c r="B126" s="179"/>
-      <c r="C126" s="179"/>
-      <c r="D126" s="179"/>
-      <c r="E126" s="179"/>
+    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="186"/>
+      <c r="B123" s="186"/>
+      <c r="C123" s="186"/>
+      <c r="D123" s="186"/>
+      <c r="E123" s="186"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="186"/>
+      <c r="B124" s="186"/>
+      <c r="C124" s="186"/>
+      <c r="D124" s="186"/>
+      <c r="E124" s="186"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="186"/>
+      <c r="B125" s="186"/>
+      <c r="C125" s="186"/>
+      <c r="D125" s="186"/>
+      <c r="E125" s="186"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="186"/>
+      <c r="B126" s="186"/>
+      <c r="C126" s="186"/>
+      <c r="D126" s="186"/>
+      <c r="E126" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A123:E126"/>
     <mergeCell ref="A117:C118"/>
@@ -3127,6 +3167,11 @@
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A109:B112"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3137,42 +3182,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3196,7 +3241,7 @@
       <c r="M2" s="27"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3211,113 +3256,113 @@
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="200" t="s">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="205" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="201"/>
-      <c r="C4" s="201"/>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="201"/>
-      <c r="I4" s="201"/>
-      <c r="J4" s="201"/>
-      <c r="K4" s="201"/>
-      <c r="L4" s="201"/>
-      <c r="M4" s="202"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="203"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="204"/>
-      <c r="G5" s="204"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="204"/>
-      <c r="L5" s="204"/>
-      <c r="M5" s="205"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="206"/>
-      <c r="B6" s="207"/>
-      <c r="C6" s="207"/>
-      <c r="D6" s="207"/>
-      <c r="E6" s="207"/>
-      <c r="F6" s="207"/>
-      <c r="G6" s="207"/>
-      <c r="H6" s="207"/>
-      <c r="I6" s="207"/>
-      <c r="J6" s="207"/>
-      <c r="K6" s="207"/>
-      <c r="L6" s="207"/>
-      <c r="M6" s="208"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="195" t="s">
+      <c r="B4" s="206"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="206"/>
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="207"/>
+    </row>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="210"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="211"/>
+      <c r="B6" s="212"/>
+      <c r="C6" s="212"/>
+      <c r="D6" s="212"/>
+      <c r="E6" s="212"/>
+      <c r="F6" s="212"/>
+      <c r="G6" s="212"/>
+      <c r="H6" s="212"/>
+      <c r="I6" s="212"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
+      <c r="M6" s="213"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="195" t="s">
+      <c r="B7" s="191" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="195" t="s">
+      <c r="C7" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="195" t="s">
+      <c r="D7" s="191" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="195" t="s">
+      <c r="E7" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="193" t="s">
+      <c r="F7" s="199" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="195" t="s">
+      <c r="G7" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="196" t="s">
+      <c r="H7" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="193" t="s">
+      <c r="I7" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="193" t="s">
+      <c r="J7" s="199" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="198" t="s">
+      <c r="K7" s="203" t="s">
         <v>58</v>
       </c>
       <c r="L7" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="191" t="s">
+      <c r="M7" s="197" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="195"/>
-      <c r="B8" s="209"/>
-      <c r="C8" s="195"/>
-      <c r="D8" s="209"/>
-      <c r="E8" s="195"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="195"/>
-      <c r="H8" s="197"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="194"/>
-      <c r="K8" s="199"/>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="191"/>
+      <c r="B8" s="192"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="192"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="200"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="200"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="204"/>
       <c r="L8" s="30" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="M8" s="191"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="197"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="69">
         <v>1</v>
       </c>
@@ -3334,14 +3379,14 @@
         <v>3.43</v>
       </c>
       <c r="F9" s="71">
-        <v>211055.01</v>
+        <v>159097.01</v>
       </c>
       <c r="G9" s="80">
-        <v>211055.01</v>
+        <v>159100</v>
       </c>
       <c r="H9" s="72">
         <f t="shared" ref="H9:H32" si="0">F9-G9</f>
-        <v>0</v>
+        <v>-2.9899999999906868</v>
       </c>
       <c r="I9" s="72">
         <f>IF(H9&gt;0,H9*3%,0)</f>
@@ -3357,17 +3402,17 @@
       </c>
       <c r="L9" s="75">
         <f t="shared" ref="L9:L32" si="1">ROUND(SUM(H9:K9),0) + N9</f>
-        <v>159097.01</v>
+        <v>159094.01</v>
       </c>
       <c r="M9" s="76">
         <f t="shared" ref="M9:M32" si="2">ROUND(L9*3%,0) + L9</f>
-        <v>163870.01</v>
+        <v>163867.01</v>
       </c>
       <c r="N9" s="20">
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="78">
         <f>A9+1</f>
         <v>2</v>
@@ -3385,11 +3430,11 @@
         <v>2.95</v>
       </c>
       <c r="F10" s="80">
-        <v>176233.02</v>
+        <v>136833.01999999999</v>
       </c>
       <c r="G10" s="80">
         <f t="shared" ref="G10:G14" si="3">F10</f>
-        <v>176233.02</v>
+        <v>136833.01999999999</v>
       </c>
       <c r="H10" s="72">
         <f t="shared" si="0"/>
@@ -3421,7 +3466,7 @@
       </c>
       <c r="O10" s="20"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="78">
         <f t="shared" ref="A11:A32" si="7">A10+1</f>
         <v>3</v>
@@ -3440,11 +3485,11 @@
         <v>6.8000000000000007</v>
       </c>
       <c r="F11" s="80">
-        <v>406231.03</v>
+        <v>324873.03000000003</v>
       </c>
       <c r="G11" s="80">
         <f t="shared" si="3"/>
-        <v>406231.03</v>
+        <v>324873.03000000003</v>
       </c>
       <c r="H11" s="72">
         <f t="shared" si="0"/>
@@ -3478,7 +3523,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="69">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3494,14 +3539,15 @@
         <v>3.43</v>
       </c>
       <c r="F12" s="71">
-        <v>199320.04</v>
+        <v>153117.04</v>
       </c>
       <c r="G12" s="80">
-        <v>205300.04</v>
+        <f t="shared" si="3"/>
+        <v>153117.04</v>
       </c>
       <c r="H12" s="72">
         <f t="shared" si="0"/>
-        <v>-5980</v>
+        <v>0</v>
       </c>
       <c r="I12" s="72">
         <f t="shared" si="4"/>
@@ -3517,11 +3563,11 @@
       </c>
       <c r="L12" s="75">
         <f t="shared" si="1"/>
-        <v>153117.04</v>
+        <v>159097.04</v>
       </c>
       <c r="M12" s="76">
         <f t="shared" si="2"/>
-        <v>157711.04000000001</v>
+        <v>163870.04</v>
       </c>
       <c r="N12" s="20">
         <f t="shared" si="8"/>
@@ -3529,7 +3575,7 @@
       </c>
       <c r="P12" s="20"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="69">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3545,11 +3591,11 @@
         <v>2.95</v>
       </c>
       <c r="F13" s="71">
-        <v>176233.05</v>
+        <v>136833.04999999999</v>
       </c>
       <c r="G13" s="80">
-        <f>F13</f>
-        <v>176233.05</v>
+        <f t="shared" si="3"/>
+        <v>136833.04999999999</v>
       </c>
       <c r="H13" s="72">
         <f t="shared" si="0"/>
@@ -3581,7 +3627,7 @@
       </c>
       <c r="P13" s="20"/>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="78">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3597,11 +3643,11 @@
         <v>5.69</v>
       </c>
       <c r="F14" s="71">
-        <v>339920.06</v>
+        <v>263925.06</v>
       </c>
       <c r="G14" s="80">
-        <f t="shared" si="3"/>
-        <v>339920.06</v>
+        <f t="shared" ref="G14:G25" si="9">F14</f>
+        <v>263925.06</v>
       </c>
       <c r="H14" s="72">
         <f t="shared" si="0"/>
@@ -3635,7 +3681,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="69">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3651,18 +3697,19 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="71">
-        <v>204908.07</v>
+        <v>370152.07</v>
       </c>
       <c r="G15" s="80">
-        <v>0</v>
+        <f>159097+211056</f>
+        <v>370153</v>
       </c>
       <c r="H15" s="72">
         <f t="shared" si="0"/>
-        <v>204908.07</v>
+        <v>-0.92999999999301508</v>
       </c>
       <c r="I15" s="72">
         <f t="shared" si="4"/>
-        <v>6147.2421000000004</v>
+        <v>0</v>
       </c>
       <c r="J15" s="73">
         <f t="shared" si="5"/>
@@ -3674,11 +3721,11 @@
       </c>
       <c r="L15" s="75">
         <f t="shared" si="1"/>
-        <v>370152.07</v>
+        <v>159096.07</v>
       </c>
       <c r="M15" s="76">
         <f t="shared" si="2"/>
-        <v>381257.07</v>
+        <v>163869.07</v>
       </c>
       <c r="N15" s="20">
         <f t="shared" si="8"/>
@@ -3688,7 +3735,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="69">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3706,16 +3753,19 @@
         <v>2.95</v>
       </c>
       <c r="F16" s="71">
-        <v>638758.07999999996</v>
-      </c>
-      <c r="G16" s="80"/>
+        <v>794753.08</v>
+      </c>
+      <c r="G16" s="80">
+        <f t="shared" si="9"/>
+        <v>794753.08</v>
+      </c>
       <c r="H16" s="72">
         <f t="shared" si="0"/>
-        <v>638758.07999999996</v>
+        <v>0</v>
       </c>
       <c r="I16" s="72">
         <f t="shared" si="4"/>
-        <v>19162.742399999999</v>
+        <v>0</v>
       </c>
       <c r="J16" s="73">
         <f t="shared" si="5"/>
@@ -3727,18 +3777,18 @@
       </c>
       <c r="L16" s="75">
         <f t="shared" si="1"/>
-        <v>794753.08</v>
+        <v>136833.07999999999</v>
       </c>
       <c r="M16" s="76">
         <f t="shared" si="2"/>
-        <v>818596.08</v>
+        <v>140938.07999999999</v>
       </c>
       <c r="N16" s="20">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="69">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3756,11 +3806,11 @@
         <v>5.69</v>
       </c>
       <c r="F17" s="71">
-        <v>339920.09</v>
+        <v>263925.09000000003</v>
       </c>
       <c r="G17" s="80">
-        <f t="shared" ref="G17:G23" si="9">F17</f>
-        <v>339920.09</v>
+        <f t="shared" si="9"/>
+        <v>263925.09000000003</v>
       </c>
       <c r="H17" s="72">
         <f t="shared" si="0"/>
@@ -3791,7 +3841,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="69">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3809,11 +3859,11 @@
         <v>3.43</v>
       </c>
       <c r="F18" s="71">
-        <v>199100.1</v>
+        <v>159097.1</v>
       </c>
       <c r="G18" s="80">
         <f t="shared" si="9"/>
-        <v>199100.1</v>
+        <v>159097.1</v>
       </c>
       <c r="H18" s="72">
         <f>F18-G18</f>
@@ -3844,7 +3894,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3862,11 +3912,11 @@
         <v>2.95</v>
       </c>
       <c r="F19" s="71">
-        <v>176233.11</v>
+        <v>136833.10999999999</v>
       </c>
       <c r="G19" s="80">
         <f t="shared" si="9"/>
-        <v>176233.11</v>
+        <v>136833.10999999999</v>
       </c>
       <c r="H19" s="72">
         <f t="shared" si="0"/>
@@ -3897,7 +3947,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3916,15 +3966,14 @@
         <v>6.2</v>
       </c>
       <c r="F20" s="71">
-        <v>371406.12</v>
+        <v>287581.12</v>
       </c>
       <c r="G20" s="80">
-        <f t="shared" si="9"/>
-        <v>371406.12</v>
+        <v>296208.12</v>
       </c>
       <c r="H20" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-8627</v>
       </c>
       <c r="I20" s="72">
         <f t="shared" si="4"/>
@@ -3940,18 +3989,18 @@
       </c>
       <c r="L20" s="75">
         <f t="shared" si="1"/>
-        <v>287581.12</v>
+        <v>278954.12</v>
       </c>
       <c r="M20" s="76">
         <f t="shared" si="2"/>
-        <v>296208.12</v>
+        <v>287323.12</v>
       </c>
       <c r="N20" s="20">
         <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="69">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3969,11 +4018,11 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="71">
-        <v>204908.13</v>
+        <v>159097.13</v>
       </c>
       <c r="G21" s="80">
         <f t="shared" si="9"/>
-        <v>204908.13</v>
+        <v>159097.13</v>
       </c>
       <c r="H21" s="72">
         <f t="shared" si="0"/>
@@ -4004,7 +4053,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="69">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -4022,11 +4071,11 @@
         <v>2.95</v>
       </c>
       <c r="F22" s="71">
-        <v>176233.14</v>
+        <v>136833.14000000001</v>
       </c>
       <c r="G22" s="80">
         <f t="shared" si="9"/>
-        <v>176233.14</v>
+        <v>136833.14000000001</v>
       </c>
       <c r="H22" s="72">
         <f t="shared" si="0"/>
@@ -4057,7 +4106,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="78">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -4076,11 +4125,11 @@
         <v>6.2</v>
       </c>
       <c r="F23" s="80">
-        <v>370387.15</v>
+        <v>287581.15000000002</v>
       </c>
       <c r="G23" s="80">
         <f t="shared" si="9"/>
-        <v>370387.15</v>
+        <v>287581.15000000002</v>
       </c>
       <c r="H23" s="72">
         <f t="shared" si="0"/>
@@ -4111,7 +4160,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="78">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -4127,14 +4176,15 @@
         <v>3.43</v>
       </c>
       <c r="F24" s="71">
-        <v>199487.16</v>
+        <v>153112.16</v>
       </c>
       <c r="G24" s="80">
-        <v>205472</v>
+        <f t="shared" si="9"/>
+        <v>153112.16</v>
       </c>
       <c r="H24" s="72">
         <f t="shared" si="0"/>
-        <v>-5984.8399999999965</v>
+        <v>0</v>
       </c>
       <c r="I24" s="72">
         <f t="shared" si="4"/>
@@ -4150,18 +4200,18 @@
       </c>
       <c r="L24" s="75">
         <f t="shared" si="1"/>
-        <v>153112.16</v>
+        <v>159097.16</v>
       </c>
       <c r="M24" s="76">
         <f t="shared" si="2"/>
-        <v>157705.16</v>
+        <v>163870.16</v>
       </c>
       <c r="N24" s="20">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="69">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -4179,11 +4229,11 @@
         <v>2.95</v>
       </c>
       <c r="F25" s="80">
-        <v>176233.17</v>
+        <v>136833.17000000001</v>
       </c>
       <c r="G25" s="80">
-        <f>F25</f>
-        <v>176233.17</v>
+        <f t="shared" si="9"/>
+        <v>136833.17000000001</v>
       </c>
       <c r="H25" s="72">
         <f t="shared" si="0"/>
@@ -4214,7 +4264,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="78">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4231,11 +4281,11 @@
         <v>6.2</v>
       </c>
       <c r="F26" s="80">
-        <v>370387.18</v>
+        <v>287581.18</v>
       </c>
       <c r="G26" s="82">
         <f>F26</f>
-        <v>370387.18</v>
+        <v>287581.18</v>
       </c>
       <c r="H26" s="72">
         <f t="shared" si="0"/>
@@ -4266,7 +4316,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="78">
         <f t="shared" si="7"/>
         <v>19</v>
@@ -4284,16 +4334,18 @@
         <v>3.43</v>
       </c>
       <c r="F27" s="80">
-        <v>1097243.19</v>
-      </c>
-      <c r="G27" s="80"/>
+        <v>1289257.19</v>
+      </c>
+      <c r="G27" s="80">
+        <v>1130160.19</v>
+      </c>
       <c r="H27" s="72">
         <f t="shared" si="0"/>
-        <v>1097243.19</v>
+        <v>159097</v>
       </c>
       <c r="I27" s="72">
         <f t="shared" si="4"/>
-        <v>32917.295699999995</v>
+        <v>4772.91</v>
       </c>
       <c r="J27" s="73">
         <f t="shared" si="5"/>
@@ -4305,18 +4357,18 @@
       </c>
       <c r="L27" s="75">
         <f t="shared" si="1"/>
-        <v>1289257.19</v>
+        <v>322967.19</v>
       </c>
       <c r="M27" s="76">
         <f t="shared" si="2"/>
-        <v>1327935.19</v>
+        <v>332656.19</v>
       </c>
       <c r="N27" s="20">
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="78">
         <f t="shared" si="7"/>
         <v>20</v>
@@ -4334,11 +4386,11 @@
         <v>2.95</v>
       </c>
       <c r="F28" s="82">
-        <v>176233.2</v>
+        <v>136833.20000000001</v>
       </c>
       <c r="G28" s="80">
         <f t="shared" ref="G28" si="10">F28</f>
-        <v>176233.2</v>
+        <v>136833.20000000001</v>
       </c>
       <c r="H28" s="72">
         <f t="shared" si="0"/>
@@ -4369,7 +4421,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="78">
         <f t="shared" si="7"/>
         <v>21</v>
@@ -4386,14 +4438,14 @@
         <v>6.2</v>
       </c>
       <c r="F29" s="82">
-        <v>360582.21</v>
+        <v>276763.21000000002</v>
       </c>
       <c r="G29" s="80">
-        <v>371400</v>
+        <v>285066.21000000002</v>
       </c>
       <c r="H29" s="72">
         <f t="shared" si="0"/>
-        <v>-10817.789999999979</v>
+        <v>-8303</v>
       </c>
       <c r="I29" s="72">
         <f t="shared" si="4"/>
@@ -4409,21 +4461,21 @@
       </c>
       <c r="L29" s="75">
         <f t="shared" si="1"/>
-        <v>276763.21000000002</v>
+        <v>279278.21000000002</v>
       </c>
       <c r="M29" s="76">
         <f t="shared" si="2"/>
-        <v>285066.21000000002</v>
+        <v>287656.21000000002</v>
       </c>
       <c r="N29" s="20">
         <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
       <c r="O29" s="79" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="78">
         <f t="shared" si="7"/>
         <v>22</v>
@@ -4441,19 +4493,16 @@
         <v>3.43</v>
       </c>
       <c r="F30" s="82">
-        <v>423713.22</v>
-      </c>
-      <c r="G30" s="82">
-        <f>200000+180000</f>
-        <v>380000</v>
-      </c>
+        <v>204122.22</v>
+      </c>
+      <c r="G30" s="82"/>
       <c r="H30" s="72">
         <f t="shared" si="0"/>
-        <v>43713.219999999972</v>
+        <v>204122.22</v>
       </c>
       <c r="I30" s="72">
         <f t="shared" si="4"/>
-        <v>1311.3965999999991</v>
+        <v>6123.6665999999996</v>
       </c>
       <c r="J30" s="73">
         <f t="shared" si="5"/>
@@ -4465,18 +4514,18 @@
       </c>
       <c r="L30" s="75">
         <f t="shared" si="1"/>
-        <v>204122.22</v>
+        <v>369343.22</v>
       </c>
       <c r="M30" s="76">
         <f t="shared" si="2"/>
-        <v>210246.22</v>
+        <v>380423.22</v>
       </c>
       <c r="N30" s="20">
         <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="78">
         <f t="shared" si="7"/>
         <v>23</v>
@@ -4494,11 +4543,11 @@
         <v>2.95</v>
       </c>
       <c r="F31" s="82">
-        <v>176233.23</v>
-      </c>
-      <c r="G31" s="82">
-        <f>F31</f>
-        <v>176233.23</v>
+        <v>136833.23000000001</v>
+      </c>
+      <c r="G31" s="80">
+        <f t="shared" ref="G31" si="11">F31</f>
+        <v>136833.23000000001</v>
       </c>
       <c r="H31" s="72">
         <f t="shared" si="0"/>
@@ -4529,7 +4578,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="69">
         <f t="shared" si="7"/>
         <v>24</v>
@@ -4545,14 +4594,15 @@
         <v>5.68</v>
       </c>
       <c r="F32" s="81">
-        <v>339322.24</v>
-      </c>
-      <c r="G32" s="82">
-        <v>349502.24</v>
+        <v>253281.24</v>
+      </c>
+      <c r="G32" s="80">
+        <f t="shared" ref="G32" si="12">F32</f>
+        <v>253281.24</v>
       </c>
       <c r="H32" s="72">
         <f t="shared" si="0"/>
-        <v>-10180</v>
+        <v>0</v>
       </c>
       <c r="I32" s="72">
         <f t="shared" si="4"/>
@@ -4568,20 +4618,20 @@
       </c>
       <c r="L32" s="75">
         <f t="shared" si="1"/>
-        <v>253281.24</v>
+        <v>263461.24</v>
       </c>
       <c r="M32" s="76">
         <f t="shared" si="2"/>
-        <v>260879.24</v>
+        <v>271365.24</v>
       </c>
       <c r="N32" s="20">
         <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="210"/>
-      <c r="B33" s="211"/>
+    <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="193"/>
+      <c r="B33" s="194"/>
       <c r="C33" s="84"/>
       <c r="D33" s="84"/>
       <c r="E33" s="70"/>
@@ -4595,140 +4645,132 @@
       <c r="M33" s="76"/>
       <c r="N33" s="20"/>
     </row>
-    <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="212" t="s">
+    <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="195" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="212"/>
-      <c r="C34" s="213"/>
+      <c r="B34" s="195"/>
+      <c r="C34" s="196"/>
       <c r="D34" s="86"/>
       <c r="E34" s="93">
-        <f t="shared" ref="E34:K34" si="11">SUM(E9:E33)</f>
+        <f t="shared" ref="E34:K34" si="13">SUM(E9:E33)</f>
         <v>99.700000000000045</v>
       </c>
       <c r="F34" s="87">
-        <f t="shared" si="11"/>
-        <v>7510281.0000000009</v>
+        <f t="shared" si="13"/>
+        <v>6645148.0000000009</v>
       </c>
       <c r="G34" s="88">
-        <f t="shared" si="11"/>
-        <v>5558621.0700000012</v>
+        <f t="shared" si="13"/>
+        <v>6298862.7000000011</v>
       </c>
       <c r="H34" s="88">
-        <f t="shared" si="11"/>
-        <v>1951659.93</v>
+        <f t="shared" si="13"/>
+        <v>346285.30000000005</v>
       </c>
       <c r="I34" s="88">
-        <f t="shared" si="11"/>
-        <v>59538.676799999994</v>
+        <f t="shared" si="13"/>
+        <v>10896.5766</v>
       </c>
       <c r="J34" s="89">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4624480.4730200013</v>
       </c>
       <c r="K34" s="88">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L34" s="90">
         <f>SUM(L9:L26)</f>
-        <v>4338595.71</v>
+        <v>3472954.7100000009</v>
       </c>
       <c r="M34" s="90">
         <f>SUM(M9:M33)</f>
-        <v>6834757.0000000009</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5131121.0000000019</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="179" t="str">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="186" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
-      <c r="F37" s="179"/>
-      <c r="G37" s="179"/>
-      <c r="H37" s="179"/>
-      <c r="I37" s="179"/>
-      <c r="J37" s="179"/>
-      <c r="K37" s="179"/>
-      <c r="L37" s="179"/>
-    </row>
-    <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="179"/>
-      <c r="D38" s="179"/>
-      <c r="E38" s="179"/>
-      <c r="F38" s="179"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="179"/>
-      <c r="I38" s="179"/>
-      <c r="J38" s="179"/>
-      <c r="K38" s="179"/>
-      <c r="L38" s="179"/>
-    </row>
-    <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="179"/>
-      <c r="D39" s="179"/>
-      <c r="E39" s="179"/>
-      <c r="F39" s="179"/>
-      <c r="G39" s="179"/>
-      <c r="H39" s="179"/>
-      <c r="I39" s="179"/>
-      <c r="J39" s="179"/>
-      <c r="K39" s="179"/>
-      <c r="L39" s="179"/>
-    </row>
-    <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="179"/>
-      <c r="D40" s="179"/>
-      <c r="E40" s="179"/>
-      <c r="F40" s="179"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
-      <c r="L40" s="179"/>
-    </row>
-    <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="179"/>
-      <c r="D41" s="179"/>
-      <c r="E41" s="179"/>
-      <c r="F41" s="179"/>
-      <c r="G41" s="179"/>
-      <c r="H41" s="179"/>
-      <c r="I41" s="179"/>
-      <c r="J41" s="179"/>
-      <c r="K41" s="179"/>
-      <c r="L41" s="179"/>
-    </row>
-    <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="179"/>
-      <c r="D42" s="179"/>
-      <c r="E42" s="179"/>
-      <c r="F42" s="179"/>
-      <c r="G42" s="179"/>
-      <c r="H42" s="179"/>
-      <c r="I42" s="179"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="179"/>
-      <c r="L42" s="179"/>
+      <c r="D37" s="186"/>
+      <c r="E37" s="186"/>
+      <c r="F37" s="186"/>
+      <c r="G37" s="186"/>
+      <c r="H37" s="186"/>
+      <c r="I37" s="186"/>
+      <c r="J37" s="186"/>
+      <c r="K37" s="186"/>
+      <c r="L37" s="186"/>
+    </row>
+    <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="186"/>
+      <c r="D38" s="186"/>
+      <c r="E38" s="186"/>
+      <c r="F38" s="186"/>
+      <c r="G38" s="186"/>
+      <c r="H38" s="186"/>
+      <c r="I38" s="186"/>
+      <c r="J38" s="186"/>
+      <c r="K38" s="186"/>
+      <c r="L38" s="186"/>
+    </row>
+    <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="186"/>
+      <c r="D39" s="186"/>
+      <c r="E39" s="186"/>
+      <c r="F39" s="186"/>
+      <c r="G39" s="186"/>
+      <c r="H39" s="186"/>
+      <c r="I39" s="186"/>
+      <c r="J39" s="186"/>
+      <c r="K39" s="186"/>
+      <c r="L39" s="186"/>
+    </row>
+    <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="186"/>
+      <c r="D40" s="186"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
+      <c r="G40" s="186"/>
+      <c r="H40" s="186"/>
+      <c r="I40" s="186"/>
+      <c r="J40" s="186"/>
+      <c r="K40" s="186"/>
+      <c r="L40" s="186"/>
+    </row>
+    <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="186"/>
+      <c r="D41" s="186"/>
+      <c r="E41" s="186"/>
+      <c r="F41" s="186"/>
+      <c r="G41" s="186"/>
+      <c r="H41" s="186"/>
+      <c r="I41" s="186"/>
+      <c r="J41" s="186"/>
+      <c r="K41" s="186"/>
+      <c r="L41" s="186"/>
+    </row>
+    <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="186"/>
+      <c r="D42" s="186"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="186"/>
+      <c r="G42" s="186"/>
+      <c r="H42" s="186"/>
+      <c r="I42" s="186"/>
+      <c r="J42" s="186"/>
+      <c r="K42" s="186"/>
+      <c r="L42" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4738,6 +4780,14 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4747,10 +4797,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="120" t="s">
         <v>139</v>
       </c>
@@ -4760,18 +4810,18 @@
       <c r="F3" s="116"/>
       <c r="G3" s="117"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="122" t="s">
         <v>140</v>
       </c>
       <c r="C4" s="123"/>
       <c r="G4" s="118"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="119"/>
       <c r="G5" s="118"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="214"/>
       <c r="C6" s="215"/>
       <c r="D6" s="215"/>
@@ -4779,7 +4829,7 @@
       <c r="F6" s="215"/>
       <c r="G6" s="216"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="214"/>
       <c r="C7" s="215"/>
       <c r="D7" s="215"/>
@@ -4787,7 +4837,7 @@
       <c r="F7" s="215"/>
       <c r="G7" s="216"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="214"/>
       <c r="C8" s="215"/>
       <c r="D8" s="215"/>
@@ -4795,7 +4845,7 @@
       <c r="F8" s="215"/>
       <c r="G8" s="216"/>
     </row>
-    <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="217"/>
       <c r="C9" s="218"/>
       <c r="D9" s="218"/>
